--- a/LEIP_game_data.xlsx
+++ b/LEIP_game_data.xlsx
@@ -13,8 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Battery" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Speed_Profiles" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routes_Reference" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charters_Reference" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ports" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Poster_Routes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charters_Reference" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ports" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -103,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -119,6 +120,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1682,6 +1686,324 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Days</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Distance (nm)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Published MWh</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Ordered ports</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Matches 835-52 group</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>SOF_BLUE</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>South of France — Blue</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>220</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Savona → Monaco → Saint-Jean-Cap-Ferrat → Nice → Antibes → Saint Tropez</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>South of France (SoF)</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Coastal weave along the Riviera</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>SOF_GREEN</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>South of France &amp; Corsica — Green</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>440</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Monaco → Calvi → Ajaccio → Saint Tropez</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>SoF to Sardinia/Corsica</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Monaco round Cap Corse to Calvi &amp; Ajaccio, open-water return to Saint Tropez. The transcript's '47-48 MWh' route.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>SARD_BLUE</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Sardinia &amp; Corsica — Blue</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>370</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Ajaccio → Calvi → Porto Vecchio → Bonifacio → Porto Cervo → Porto Rotondo → Olbia</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Sardinia &amp; Corsica</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Corsica circuit into the Costa Smeralda cluster; leg order from map, direction to confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>SARD_GREEN</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Sardinia to Italy — Green</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>390</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Porto Vecchio → Porto Rotondo → Olbia → Naples → Ponte Persica → Salerno</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Deck note: tuned from 53.9 to 50 MWh by removing 24 anchor-hours and 11 nm at cruise speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>BALEARICS</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Balearics</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>380</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Port d'Andratx → Eivissa → Palma</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Baleriacs</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Andratx to Eivissa (island circumnavigation) returning to Palma</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>GREECE</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Athens → Santorini → Livadia</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Athens to Santorini and Livadia; map shows return strand toward Athens</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>TURKEY</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>295</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Gulluk → Bodrum → Gocek</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Gulluk to Bodrum, Gulf of Gokova coastal loop to Gocek</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2638,7 +2960,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
